--- a/Scenario Files/TestScenarios.xlsx
+++ b/Scenario Files/TestScenarios.xlsx
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the dryer?</t>
+          <t>It's just past 5 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the washer?</t>
+          <t>It's just past 5 PM. When should I run the washer?</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's late afternoon, around 4, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning, when should I run the dryer?</t>
+          <t>It's past 1 in the morning. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>It's just past midnight, when should I run the dishwasher?</t>
+          <t>It's just past midnight. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dryer. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dryer. When should I run it?</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>It's around 8 at night, when should I run the dishwasher?</t>
+          <t>It's around 8 at night. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
